--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <r>
       <t>n</t>
@@ -136,6 +136,88 @@
   </si>
   <si>
     <t>ButtonInteractable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CookBlockLogic</t>
+  </si>
+  <si>
+    <t>Prefabs/BlockLogic/CookBlockLogic</t>
+  </si>
+  <si>
+    <t>Prefabs/BlockLogic/MoveBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopItemBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/BlockLogic/PopItemBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PushItemBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/BlockLogic/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PushItemBlockLogic</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RotateLeftBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/BlockLogic/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RotateLeftBlockLogic</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RotateRightBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/BlockLogic/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RotateRightBlockLogic</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -410,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -441,9 +523,58 @@
         <v>22</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453704D3-94EB-43E6-AA33-447189870C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12930"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <r>
       <t>n</t>
@@ -220,11 +221,25 @@
     <t>MoveBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Prefabs/UI/StageClearPopup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/UI/StageSelectPopup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageSelectPopup</t>
+  </si>
+  <si>
+    <t>StageClearPopup</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -274,9 +289,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -491,8 +506,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -571,6 +586,22 @@
         <v>34</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -579,7 +610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453704D3-94EB-43E6-AA33-447189870C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <r>
       <t>n</t>
@@ -235,11 +234,30 @@
   <si>
     <t>StageClearPopup</t>
   </si>
+  <si>
+    <t>ButtonToggle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RotateBackBlockLogic</t>
+  </si>
+  <si>
+    <t>Prefabs/BlockLogic/RotateBackBlockLogic</t>
+  </si>
+  <si>
+    <t>DashBlockLogic</t>
+  </si>
+  <si>
+    <t>Prefabs/BlockLogic/DashBlockLogic</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/ButtonToggle</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -506,8 +524,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -556,50 +574,74 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -610,7 +652,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <r>
       <t>n</t>
@@ -221,14 +221,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/UI/StageClearPopup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/UI/StageSelectPopup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>StageSelectPopup</t>
   </si>
   <si>
@@ -251,7 +243,19 @@
     <t>Prefabs/BlockLogic/DashBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/UI/ButtonToggle</t>
+    <t>Prefabs/WorldUI/Elements/Toggle</t>
+  </si>
+  <si>
+    <t>ChapterSelectPopup</t>
+  </si>
+  <si>
+    <t>Prefabs/WorldUI/ChapterSelectPopup</t>
+  </si>
+  <si>
+    <t>Prefabs/WorldUI/StageClearPopup</t>
+  </si>
+  <si>
+    <t>Prefabs/WorldUI/StageSelectPopup</t>
   </si>
 </sst>
 </file>
@@ -525,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -574,10 +578,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -614,34 +618,42 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
-        <v>45</v>
+      <c r="B15" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <r>
       <t>n</t>
@@ -256,6 +256,20 @@
   </si>
   <si>
     <t>Prefabs/WorldUI/StageSelectPopup</t>
+  </si>
+  <si>
+    <t>NPCMessagePopup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/WorldUI/NPCMessagePopup</t>
+  </si>
+  <si>
+    <t>Prefabs/WorldUI/RecipePopup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecipePopup</t>
   </si>
 </sst>
 </file>
@@ -529,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -650,9 +664,25 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" t="s">
         <v>43</v>
       </c>
     </row>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
   <si>
     <r>
       <t>n</t>
@@ -135,10 +135,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ButtonInteractable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CookBlockLogic</t>
   </si>
   <si>
@@ -270,6 +266,17 @@
   </si>
   <si>
     <t>RecipePopup</t>
+  </si>
+  <si>
+    <t>ButtonInteractable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Tile</t>
+  </si>
+  <si>
+    <t>Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -543,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -568,7 +575,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>22</v>
@@ -576,114 +583,122 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>41</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -272,10 +272,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Prefabs/Tile</t>
-  </si>
-  <si>
-    <t>Tile</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -695,10 +696,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
         <v>53</v>
-      </c>
-      <c r="B18" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\dev\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <r>
       <t>n</t>
@@ -277,6 +277,13 @@
   </si>
   <si>
     <t>Prefabs/Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResetMat</t>
+  </si>
+  <si>
+    <t>Materials/Logic/ResetMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -711,7 +718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -798,6 +805,14 @@
         <v>12</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -9,18 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
     <sheet name="Material" sheetId="14" r:id="rId2"/>
+    <sheet name="Sprite" sheetId="15" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
   <si>
     <r>
       <t>n</t>
@@ -65,9 +66,6 @@
     <t>LogicBlock</t>
   </si>
   <si>
-    <t>Prefabs/LogicBlock</t>
-  </si>
-  <si>
     <t>RotateRightMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -84,135 +82,37 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/PopItemMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/PushItemMat</t>
-  </si>
-  <si>
-    <t>Materials/Logic/CookMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/MoveMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/RotateRightMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateLeftMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/RotateLeftMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/ClearMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>StartMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/StartMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TempMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/TempMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/ButtonInteractable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CookBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/CookBlockLogic</t>
-  </si>
-  <si>
-    <t>Prefabs/BlockLogic/MoveBlockLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PopItemBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/PopItemBlockLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PushItemBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/BlockLogic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PushItemBlockLogic</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateLeftBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/BlockLogic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RotateLeftBlockLogic</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateRightBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/BlockLogic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RotateRightBlockLogic</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MoveBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -230,41 +130,16 @@
     <t>RotateBackBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/RotateBackBlockLogic</t>
-  </si>
-  <si>
     <t>DashBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/DashBlockLogic</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/Elements/Toggle</t>
-  </si>
-  <si>
     <t>ChapterSelectPopup</t>
   </si>
   <si>
-    <t>Prefabs/WorldUI/ChapterSelectPopup</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/StageClearPopup</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/StageSelectPopup</t>
-  </si>
-  <si>
     <t>NPCMessagePopup</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/WorldUI/NPCMessagePopup</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/RecipePopup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RecipePopup</t>
   </si>
   <si>
@@ -276,8 +151,131 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Wall_Image</t>
+  </si>
+  <si>
+    <t>Walking_Pass_Image</t>
+  </si>
+  <si>
+    <t>Walking_Image</t>
+  </si>
+  <si>
+    <t>Table_Image</t>
+  </si>
+  <si>
+    <t>Ingredient_Image</t>
+  </si>
+  <si>
+    <t>Customer_Image</t>
+  </si>
+  <si>
+    <t>Cooking_Image</t>
+  </si>
+  <si>
+    <t>CookedFood_Image</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/CookedFood_Image.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Cooking_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Customer_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Ingredient_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Table_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Pass_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Wall_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/ClearMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/CookMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/MoveMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/PopItemMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/PushItemMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateLeftMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateRightMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/StartMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/TempMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/ButtonInteractable.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/LogicBlock.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/ChapterSelectPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/NPCMessagePopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/RecipePopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageClearPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageSelectPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/CookBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/DashBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/MoveBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PopItemBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PushItemBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateBackBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateLeftBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateRightBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/Toggle.prefab</t>
   </si>
 </sst>
 </file>
@@ -571,135 +569,135 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -728,18 +726,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -747,39 +745,39 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -787,15 +785,15 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -803,4 +801,113 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="84.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA6E936-DC69-41BC-8B60-AAE7AA4FA2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -281,7 +282,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -548,7 +549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -708,7 +709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -804,7 +805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -9,18 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
     <sheet name="Material" sheetId="14" r:id="rId2"/>
+    <sheet name="Sprite" sheetId="15" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
   <si>
     <r>
       <t>n</t>
@@ -65,9 +66,6 @@
     <t>LogicBlock</t>
   </si>
   <si>
-    <t>Prefabs/LogicBlock</t>
-  </si>
-  <si>
     <t>RotateRightMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -84,135 +82,37 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/PopItemMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/PushItemMat</t>
-  </si>
-  <si>
-    <t>Materials/Logic/CookMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/MoveMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/RotateRightMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateLeftMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/RotateLeftMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Materials/Logic/ClearMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>StartMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/StartMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TempMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Materials/Logic/TempMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/ButtonInteractable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CookBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/CookBlockLogic</t>
-  </si>
-  <si>
-    <t>Prefabs/BlockLogic/MoveBlockLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PopItemBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/PopItemBlockLogic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PushItemBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/BlockLogic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PushItemBlockLogic</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateLeftBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/BlockLogic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RotateLeftBlockLogic</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateRightBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Prefabs/BlockLogic/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RotateRightBlockLogic</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>MoveBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -230,41 +130,16 @@
     <t>RotateBackBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/RotateBackBlockLogic</t>
-  </si>
-  <si>
     <t>DashBlockLogic</t>
   </si>
   <si>
-    <t>Prefabs/BlockLogic/DashBlockLogic</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/Elements/Toggle</t>
-  </si>
-  <si>
     <t>ChapterSelectPopup</t>
   </si>
   <si>
-    <t>Prefabs/WorldUI/ChapterSelectPopup</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/StageClearPopup</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/StageSelectPopup</t>
-  </si>
-  <si>
     <t>NPCMessagePopup</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/WorldUI/NPCMessagePopup</t>
-  </si>
-  <si>
-    <t>Prefabs/WorldUI/RecipePopup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RecipePopup</t>
   </si>
   <si>
@@ -276,15 +151,138 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>Wall_Image</t>
+  </si>
+  <si>
+    <t>Walking_Pass_Image</t>
+  </si>
+  <si>
+    <t>Walking_Image</t>
+  </si>
+  <si>
+    <t>Table_Image</t>
+  </si>
+  <si>
+    <t>Ingredient_Image</t>
+  </si>
+  <si>
+    <t>Customer_Image</t>
+  </si>
+  <si>
+    <t>Cooking_Image</t>
+  </si>
+  <si>
+    <t>CookedFood_Image</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/CookedFood_Image.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Cooking_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Customer_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Ingredient_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Table_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Pass_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Wall_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/ClearMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/CookMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/MoveMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/PopItemMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/PushItemMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateLeftMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateRightMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/StartMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/TempMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/ButtonInteractable.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/LogicBlock.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/ChapterSelectPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/NPCMessagePopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/RecipePopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageClearPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageSelectPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/CookBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/DashBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/MoveBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PopItemBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PushItemBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateBackBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateLeftBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateRightBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/Toggle.prefab</t>
   </si>
   <si>
     <t>ResetMat</t>
-  </si>
-  <si>
-    <t>Materials/Logic/ResetMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/ResetMat.mat</t>
   </si>
 </sst>
 </file>
@@ -578,135 +576,135 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -735,18 +733,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -754,39 +752,39 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -794,23 +792,23 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -818,4 +816,113 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="84.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA6E936-DC69-41BC-8B60-AAE7AA4FA2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="76">
   <si>
     <r>
       <t>n</t>
@@ -278,11 +277,34 @@
   <si>
     <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/Toggle.prefab</t>
   </si>
+  <si>
+    <t>DashMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepeatMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResetMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/ResetMat.mat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ErrorWarning</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/UI/ErrorWarning.prefab</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -549,7 +571,295 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="84.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="84.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -567,262 +877,6 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="84.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="84.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
   <si>
     <r>
       <t>n</t>
@@ -299,6 +299,151 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/UI/ErrorWarning.prefab</t>
+  </si>
+  <si>
+    <t>Customer_Tile</t>
+  </si>
+  <si>
+    <t>Walking_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walking_Pass_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CookedFood_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingredient_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooking_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/CookedFood_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Cooking_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Customer_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Ingredient_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Table_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Walking_Pass_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Walking_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Wall_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Object_Food_Poke</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Hamburger_Set</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Cut_Potato</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Object_Food_Cut_Shirimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Pot_Rice_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Frier_Shirimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Object_Food_Potato</t>
+  </si>
+  <si>
+    <t>Object_Food_Tuna</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Rice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Fish</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Shirimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Fish.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Potato.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Shirimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Fish.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Frier_Shirimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Hamburger_Set.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Poke.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice_2.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Potato.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Rice.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Shirimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Tuna.prefab</t>
   </si>
 </sst>
 </file>
@@ -572,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -729,6 +874,174 @@
       </c>
       <c r="B19" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="131">
   <si>
     <r>
       <t>n</t>
@@ -444,6 +444,45 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Tuna.prefab</t>
+  </si>
+  <si>
+    <t>Image_Food_Poke</t>
+  </si>
+  <si>
+    <t>Image_Food_Hamburger_Set</t>
+  </si>
+  <si>
+    <t>Image_Food_Cut_Potato</t>
+  </si>
+  <si>
+    <t>Image_Food_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Image_Food_Cut_Shirimp</t>
+  </si>
+  <si>
+    <t>Image_Food_Pot_Rice_2</t>
+  </si>
+  <si>
+    <t>Image_Food_Frier_Shirimp</t>
+  </si>
+  <si>
+    <t>Image_Food_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Image_Food_Potato</t>
+  </si>
+  <si>
+    <t>Image_Food_Tuna</t>
+  </si>
+  <si>
+    <t>Image_Food_Rice</t>
+  </si>
+  <si>
+    <t>Image_Food_Fish</t>
+  </si>
+  <si>
+    <t>Image_Food_Shirimp</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1253,26 +1292,73 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="B10" s="1"/>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+    </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
       <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>122</v>
+      </c>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>124</v>
+      </c>
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\dev\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="120">
   <si>
     <r>
       <t>n</t>
@@ -444,6 +444,13 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Tuna.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/MemoMat.mat</t>
+  </si>
+  <si>
+    <t>MemoMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1053,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1162,6 +1169,14 @@
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="133">
   <si>
     <r>
       <t>n</t>
@@ -483,6 +483,13 @@
   </si>
   <si>
     <t>Image_Food_Shirimp</t>
+  </si>
+  <si>
+    <t>MemoMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/MemoMat.mat</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1201,6 +1208,14 @@
       </c>
       <c r="B13" s="1" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
   <si>
     <r>
       <t>n</t>
@@ -127,369 +127,401 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>DashBlockLogic</t>
+  </si>
+  <si>
+    <t>ChapterSelectPopup</t>
+  </si>
+  <si>
+    <t>NPCMessagePopup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecipePopup</t>
+  </si>
+  <si>
+    <t>ButtonInteractable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall_Image</t>
+  </si>
+  <si>
+    <t>Walking_Pass_Image</t>
+  </si>
+  <si>
+    <t>Walking_Image</t>
+  </si>
+  <si>
+    <t>Table_Image</t>
+  </si>
+  <si>
+    <t>Ingredient_Image</t>
+  </si>
+  <si>
+    <t>Customer_Image</t>
+  </si>
+  <si>
+    <t>Cooking_Image</t>
+  </si>
+  <si>
+    <t>CookedFood_Image</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/CookedFood_Image.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Cooking_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Customer_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Ingredient_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Table_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Pass_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Tile/Wall_Image.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/ClearMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/CookMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/MoveMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/PopItemMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/PushItemMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateLeftMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateRightMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/StartMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/TempMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/ButtonInteractable.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/LogicBlock.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/ChapterSelectPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/NPCMessagePopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/RecipePopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageClearPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageSelectPopup.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/CookBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/DashBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/MoveBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PopItemBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PushItemBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateBackBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateLeftBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateRightBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/Toggle.prefab</t>
+  </si>
+  <si>
+    <t>DashMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepeatMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResetMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/ResetMat.mat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ErrorWarning</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/UI/ErrorWarning.prefab</t>
+  </si>
+  <si>
+    <t>Customer_Tile</t>
+  </si>
+  <si>
+    <t>Walking_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wall_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walking_Pass_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CookedFood_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingredient_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooking_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table_Tile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/CookedFood_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Cooking_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Customer_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Ingredient_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Table_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Walking_Pass_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Walking_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Wall_Tile.prefab</t>
+  </si>
+  <si>
+    <t>Object_Food_Poke</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Hamburger_Set</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Cut_Potato</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Object_Food_Cut_Shirimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Pot_Rice_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Frier_Shirimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Object_Food_Potato</t>
+  </si>
+  <si>
+    <t>Object_Food_Tuna</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Rice</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Fish</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object_Food_Shirimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Fish.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Potato.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Shirimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Fish.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Frier_Shirimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Hamburger_Set.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Poke.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice_2.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Potato.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Rice.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Shirimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Tuna.prefab</t>
+  </si>
+  <si>
+    <t>Image_Food_Poke</t>
+  </si>
+  <si>
+    <t>Image_Food_Hamburger_Set</t>
+  </si>
+  <si>
+    <t>Image_Food_Cut_Potato</t>
+  </si>
+  <si>
+    <t>Image_Food_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Image_Food_Cut_Shirimp</t>
+  </si>
+  <si>
+    <t>Image_Food_Pot_Rice_2</t>
+  </si>
+  <si>
+    <t>Image_Food_Frier_Shirimp</t>
+  </si>
+  <si>
+    <t>Image_Food_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Image_Food_Potato</t>
+  </si>
+  <si>
+    <t>Image_Food_Tuna</t>
+  </si>
+  <si>
+    <t>Image_Food_Rice</t>
+  </si>
+  <si>
+    <t>Image_Food_Fish</t>
+  </si>
+  <si>
+    <t>Image_Food_Shirimp</t>
+  </si>
+  <si>
+    <t>MemoMat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/MemoMat.mat</t>
+  </si>
+  <si>
+    <t>Function</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>RotateBack</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mat</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/TempMat.mat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>RotateBackBlockLogic</t>
-  </si>
-  <si>
-    <t>DashBlockLogic</t>
-  </si>
-  <si>
-    <t>ChapterSelectPopup</t>
-  </si>
-  <si>
-    <t>NPCMessagePopup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecipePopup</t>
-  </si>
-  <si>
-    <t>ButtonInteractable</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wall_Image</t>
-  </si>
-  <si>
-    <t>Walking_Pass_Image</t>
-  </si>
-  <si>
-    <t>Walking_Image</t>
-  </si>
-  <si>
-    <t>Table_Image</t>
-  </si>
-  <si>
-    <t>Ingredient_Image</t>
-  </si>
-  <si>
-    <t>Customer_Image</t>
-  </si>
-  <si>
-    <t>Cooking_Image</t>
-  </si>
-  <si>
-    <t>CookedFood_Image</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/CookedFood_Image.png</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Cooking_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Customer_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Ingredient_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Table_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Walking_Pass_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Textures/Tile/Wall_Image.png</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/ClearMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/CookMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/MoveMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/PopItemMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/PushItemMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/RotateLeftMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/RotateRightMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/StartMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/TempMat.mat</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/ButtonInteractable.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/LogicBlock.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/ChapterSelectPopup.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/NPCMessagePopup.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/RecipePopup.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageClearPopup.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageSelectPopup.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/CookBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/DashBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/MoveBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PopItemBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/PushItemBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateBackBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateLeftBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RotateRightBlockLogic.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/Toggle.prefab</t>
-  </si>
-  <si>
-    <t>DashMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RepeatMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResetMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/ResetMat.mat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ErrorWarning</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/UI/ErrorWarning.prefab</t>
-  </si>
-  <si>
-    <t>Customer_Tile</t>
-  </si>
-  <si>
-    <t>Walking_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wall_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Walking_Pass_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CookedFood_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingredient_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cooking_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table_Tile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/CookedFood_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Cooking_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Customer_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Ingredient_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Table_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Walking_Pass_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Walking_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Tiles/Wall_Tile.prefab</t>
-  </si>
-  <si>
-    <t>Object_Food_Poke</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Hamburger_Set</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Cut_Potato</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Pot_Rice</t>
-  </si>
-  <si>
-    <t>Object_Food_Cut_Shirimp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Pot_Rice_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Frier_Shirimp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Cut_Fish</t>
-  </si>
-  <si>
-    <t>Object_Food_Potato</t>
-  </si>
-  <si>
-    <t>Object_Food_Tuna</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Rice</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Fish</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Shirimp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Fish.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Potato.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Shirimp.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Fish.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Frier_Shirimp.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Hamburger_Set.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Poke.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice_2.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Potato.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Rice.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Shirimp.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Tuna.prefab</t>
-  </si>
-  <si>
-    <t>Image_Food_Poke</t>
-  </si>
-  <si>
-    <t>Image_Food_Hamburger_Set</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Potato</t>
-  </si>
-  <si>
-    <t>Image_Food_Pot_Rice</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Shirimp</t>
-  </si>
-  <si>
-    <t>Image_Food_Pot_Rice_2</t>
-  </si>
-  <si>
-    <t>Image_Food_Frier_Shirimp</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Fish</t>
-  </si>
-  <si>
-    <t>Image_Food_Potato</t>
-  </si>
-  <si>
-    <t>Image_Food_Tuna</t>
-  </si>
-  <si>
-    <t>Image_Food_Rice</t>
-  </si>
-  <si>
-    <t>Image_Food_Fish</t>
-  </si>
-  <si>
-    <t>Image_Food_Shirimp</t>
-  </si>
-  <si>
-    <t>MemoMat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/MemoMat.mat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepeatBlockLogic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RepeatBlockLogic.prefab</t>
   </si>
 </sst>
 </file>
@@ -763,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -783,15 +815,15 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -799,7 +831,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -807,15 +839,15 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -823,7 +855,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -831,7 +863,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -839,7 +871,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -847,156 +879,156 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>21</v>
+      <c r="A11" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
+      <c r="A12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" s="1" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>76</v>
+      <c r="A24" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>81</v>
+      <c r="A25" t="s">
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B29" t="s">
         <v>110</v>
@@ -1004,90 +1036,98 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
-      <c r="B30" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" t="s">
-        <v>107</v>
+      <c r="B32" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>105</v>
+      <c r="A35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" t="s">
-        <v>114</v>
+        <v>98</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>101</v>
+      <c r="A37" t="s">
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1099,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1119,7 +1159,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1127,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1135,7 +1175,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1143,7 +1183,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1151,7 +1191,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1159,20 +1199,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>47</v>
@@ -1180,42 +1220,58 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" t="s">
         <v>131</v>
-      </c>
-      <c r="B14" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1244,135 +1300,135 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="140">
   <si>
     <r>
       <t>n</t>
@@ -522,6 +522,13 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RepeatBlockLogic.prefab</t>
+  </si>
+  <si>
+    <t>Assets/_MoonSooAsset/Prefabs/RepeatSheets.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepeatSheets</t>
   </si>
 </sst>
 </file>
@@ -795,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1128,6 +1135,14 @@
       </c>
       <c r="B41" t="s">
         <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -524,11 +524,11 @@
     <t>Assets/Resources_Addressable/Prefabs/BlockLogic/RepeatBlockLogic.prefab</t>
   </si>
   <si>
-    <t>Assets/_MoonSooAsset/Prefabs/RepeatSheets.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>RepeatSheets</t>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Sheet/RepeatSheet.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RepeatSheet</t>
   </si>
 </sst>
 </file>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
   <si>
     <r>
       <t>n</t>
@@ -353,96 +353,6 @@
     <t>Assets/Resources_Addressable/Prefabs/Tiles/Wall_Tile.prefab</t>
   </si>
   <si>
-    <t>Object_Food_Poke</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Hamburger_Set</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Cut_Potato</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Pot_Rice</t>
-  </si>
-  <si>
-    <t>Object_Food_Cut_Shirimp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Pot_Rice_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Frier_Shirimp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Cut_Fish</t>
-  </si>
-  <si>
-    <t>Object_Food_Potato</t>
-  </si>
-  <si>
-    <t>Object_Food_Tuna</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Rice</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Fish</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object_Food_Shirimp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Fish.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Potato.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Cut_Shirimp.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Fish.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Frier_Shirimp.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Hamburger_Set.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Poke.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Pot_Rice_2.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Potato.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Rice.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Shirimp.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/Items/Object_Food_Tuna.prefab</t>
-  </si>
-  <si>
     <t>Image_Food_Poke</t>
   </si>
   <si>
@@ -529,6 +439,61 @@
   </si>
   <si>
     <t>RepeatSheet</t>
+  </si>
+  <si>
+    <t>Prefab_Shrimp</t>
+  </si>
+  <si>
+    <t>Prefab_Rice</t>
+  </si>
+  <si>
+    <t>Prefab_Fish</t>
+  </si>
+  <si>
+    <t>Prefab_Fryer_Shrimp</t>
+  </si>
+  <si>
+    <t>Prefab_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Prefab_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Prefab_Ebidon</t>
+  </si>
+  <si>
+    <t>Prefab_Sushi_Shrimp</t>
+  </si>
+  <si>
+    <t>Prefab_Cut_Shrimp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Fish.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Rice.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Pot_Rice.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Cut_Fish.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Ebidon.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Shrimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Cut_Shrimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Fryer_Shrimp.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Sushi_Shrimp.prefab</t>
   </si>
 </sst>
 </file>
@@ -571,7 +536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -579,14 +544,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -802,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -810,339 +796,307 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>137</v>
+      <c r="A12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" t="s">
-        <v>110</v>
+      <c r="A29" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
+      <c r="A30" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" t="s">
-        <v>105</v>
+      <c r="A31" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>111</v>
+      <c r="A32" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" t="s">
-        <v>106</v>
+      <c r="A33" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="A34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>139</v>
-      </c>
-      <c r="B42" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1219,10 +1173,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1267,7 +1221,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>51</v>
@@ -1283,10 +1237,10 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1379,71 +1333,71 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
   <si>
     <r>
       <t>n</t>
@@ -494,6 +494,27 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/Items/Prefab_Sushi_Shrimp.prefab</t>
+  </si>
+  <si>
+    <t>FunctionMat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/FunctionMat.mat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Sheet/FunctionSheet.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionSheet</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockLogic/FunctionBlockLogic.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionBlockLogic</t>
   </si>
 </sst>
 </file>
@@ -788,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -893,210 +914,226 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>55</v>
+        <v>137</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>58</v>
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B29" s="4" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>126</v>
+        <v>116</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B38" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1241,6 +1278,14 @@
       </c>
       <c r="B16" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\dev\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="148">
   <si>
     <r>
       <t>n</t>
@@ -516,12 +516,42 @@
   <si>
     <t>FunctionBlockLogic</t>
   </si>
+  <si>
+    <t>Icon_Cooking_Tile_Cut</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Pot</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Fan</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Frier</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Tray</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Cut.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Frier.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Pot.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Tray.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Fan.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -542,6 +572,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Nanum Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -557,7 +593,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -580,11 +616,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -592,6 +643,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -809,14 +863,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="84.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -824,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -832,7 +886,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
@@ -840,7 +894,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -848,7 +902,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -856,7 +910,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
@@ -864,7 +918,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -872,7 +926,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -880,7 +934,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -888,7 +942,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -896,7 +950,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
         <v>109</v>
       </c>
@@ -904,7 +958,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
         <v>110</v>
       </c>
@@ -912,7 +966,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>137</v>
       </c>
@@ -920,7 +974,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -928,7 +982,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -936,7 +990,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -944,7 +998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
@@ -952,7 +1006,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
@@ -960,7 +1014,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -968,7 +1022,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
         <v>26</v>
       </c>
@@ -976,7 +1030,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
         <v>73</v>
       </c>
@@ -984,7 +1038,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
         <v>76</v>
       </c>
@@ -992,7 +1046,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
         <v>77</v>
       </c>
@@ -1000,7 +1054,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
@@ -1008,7 +1062,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
         <v>79</v>
       </c>
@@ -1016,7 +1070,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="4" t="s">
         <v>75</v>
       </c>
@@ -1024,7 +1078,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
         <v>80</v>
       </c>
@@ -1032,7 +1086,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
         <v>81</v>
       </c>
@@ -1040,7 +1094,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
@@ -1048,7 +1102,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" s="6" t="s">
         <v>115</v>
       </c>
@@ -1056,7 +1110,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
         <v>118</v>
       </c>
@@ -1064,7 +1118,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
         <v>116</v>
       </c>
@@ -1072,7 +1126,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
         <v>119</v>
       </c>
@@ -1080,7 +1134,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
         <v>120</v>
       </c>
@@ -1088,7 +1142,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
         <v>114</v>
       </c>
@@ -1096,7 +1150,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
         <v>122</v>
       </c>
@@ -1104,7 +1158,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
         <v>117</v>
       </c>
@@ -1112,7 +1166,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
         <v>121</v>
       </c>
@@ -1120,7 +1174,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="4" t="s">
         <v>113</v>
       </c>
@@ -1128,12 +1182,52 @@
         <v>112</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="13.5" thickBot="1">
       <c r="A40" s="4" t="s">
         <v>135</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="13.5" thickBot="1">
+      <c r="A41" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="13.5" thickBot="1">
+      <c r="A42" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="13.5" thickBot="1">
+      <c r="A43" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B43" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="13.5" thickBot="1">
+      <c r="A44" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="13.5" thickBot="1">
+      <c r="A45" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1146,13 +1240,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="84.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1160,7 +1254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1168,7 +1262,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1176,7 +1270,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1184,7 +1278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,7 +1286,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,7 +1294,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1208,7 +1302,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>107</v>
       </c>
@@ -1216,7 +1310,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,7 +1318,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1232,7 +1326,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1240,7 +1334,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>71</v>
       </c>
@@ -1248,7 +1342,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>69</v>
       </c>
@@ -1256,7 +1350,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>106</v>
       </c>
@@ -1264,7 +1358,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>70</v>
       </c>
@@ -1272,7 +1366,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>104</v>
       </c>
@@ -1280,7 +1374,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>132</v>
       </c>
@@ -1298,13 +1392,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="84.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1312,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1320,7 +1414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1328,7 +1422,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1336,7 +1430,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -1344,7 +1438,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1352,7 +1446,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1360,7 +1454,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1368,7 +1462,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1376,71 +1470,71 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>94</v>
       </c>
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>95</v>
       </c>
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>97</v>
       </c>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
         <v>103</v>
       </c>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\KHT\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="143">
   <si>
     <r>
       <t>n</t>
@@ -353,45 +353,6 @@
     <t>Assets/Resources_Addressable/Prefabs/Tiles/Wall_Tile.prefab</t>
   </si>
   <si>
-    <t>Image_Food_Poke</t>
-  </si>
-  <si>
-    <t>Image_Food_Hamburger_Set</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Potato</t>
-  </si>
-  <si>
-    <t>Image_Food_Pot_Rice</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Shirimp</t>
-  </si>
-  <si>
-    <t>Image_Food_Pot_Rice_2</t>
-  </si>
-  <si>
-    <t>Image_Food_Frier_Shirimp</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Fish</t>
-  </si>
-  <si>
-    <t>Image_Food_Potato</t>
-  </si>
-  <si>
-    <t>Image_Food_Tuna</t>
-  </si>
-  <si>
-    <t>Image_Food_Rice</t>
-  </si>
-  <si>
-    <t>Image_Food_Fish</t>
-  </si>
-  <si>
-    <t>Image_Food_Shirimp</t>
-  </si>
-  <si>
     <t>MemoMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -515,6 +476,60 @@
   </si>
   <si>
     <t>FunctionBlockLogic</t>
+  </si>
+  <si>
+    <t>Icon_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Cut_Fish.png</t>
+  </si>
+  <si>
+    <t>Icon_Cut_Shrimp</t>
+  </si>
+  <si>
+    <t>Icon_Ebidon</t>
+  </si>
+  <si>
+    <t>Icon_Fish</t>
+  </si>
+  <si>
+    <t>Icon_Fryer_Shrimp</t>
+  </si>
+  <si>
+    <t>Icon_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Icon_Rice</t>
+  </si>
+  <si>
+    <t>Icon_Shrimp</t>
+  </si>
+  <si>
+    <t>Icon_Sushi_Shrimp</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Cut_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Ebidon.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Fish.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Fryer_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Pot_Rice.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Rice.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Sushi_Shrimp.png</t>
   </si>
 </sst>
 </file>
@@ -898,7 +913,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>65</v>
@@ -906,18 +921,18 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -1050,90 +1065,90 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1210,10 +1225,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1258,7 +1273,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>51</v>
@@ -1274,18 +1289,18 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1297,7 +1312,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1378,71 +1393,74 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>127</v>
+      </c>
+      <c r="B11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>128</v>
+      </c>
+      <c r="B12" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="1"/>
+        <v>129</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>96</v>
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>103</v>
+        <v>134</v>
+      </c>
+      <c r="B18" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="148">
   <si>
     <r>
       <t>n</t>
@@ -137,9 +137,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>RecipePopup</t>
-  </si>
-  <si>
     <t>ButtonInteractable</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -237,9 +234,6 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/WorldUI/NPCMessagePopup.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Resources_Addressable/Prefabs/WorldUI/RecipePopup.prefab</t>
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/WorldUI/StageClearPopup.prefab</t>
@@ -515,6 +509,48 @@
   </si>
   <si>
     <t>FunctionBlockLogic</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/LevelPopup.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelPopup</t>
+  </si>
+  <si>
+    <t>RecipeElement</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/RecipeElement.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/RecipeUnit_ClearUIElement.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecipeUnit_ClearUIElement</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/ServingUnitUIElement.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ServingUnitUIElement</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/ArriveUnitUIElement.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArriveUnitUIElement</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/RecipeUnitUIElement.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecipeUnitUIElement</t>
   </si>
 </sst>
 </file>
@@ -809,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -829,15 +865,15 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -845,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -853,7 +889,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -861,7 +897,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -869,7 +905,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -877,7 +913,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -885,7 +921,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -893,31 +929,31 @@
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -925,7 +961,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -933,7 +969,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
@@ -941,7 +977,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -949,15 +985,15 @@
         <v>23</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -965,175 +1001,215 @@
         <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1241,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1173,7 +1249,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1181,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1189,7 +1265,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1197,7 +1273,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1205,15 +1281,15 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1221,7 +1297,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1229,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1237,55 +1313,55 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1314,135 +1390,135 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3374F85B-26D8-411E-A0D2-9E48CE4FBF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
   <si>
     <r>
       <t>n</t>
@@ -552,11 +553,17 @@
   <si>
     <t>RecipeUnitUIElement</t>
   </si>
+  <si>
+    <t>IngredientUIElement</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/IngredientUIElement.prefab</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -844,8 +851,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1212,6 +1219,14 @@
         <v>140</v>
       </c>
     </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1220,7 +1235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1372,7 +1387,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3374F85B-26D8-411E-A0D2-9E48CE4FBF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="178">
   <si>
     <r>
       <t>n</t>
@@ -559,12 +558,96 @@
   <si>
     <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/IngredientUIElement.prefab</t>
   </si>
+  <si>
+    <t>Icon_Cut_Fish</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Cut_Fish.png</t>
+  </si>
+  <si>
+    <t>Icon_Cut_Shrimp</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Cut_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Icon_Ebidon</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Ebidon.png</t>
+  </si>
+  <si>
+    <t>Icon_Fish</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Fish.png</t>
+  </si>
+  <si>
+    <t>Icon_Fryer_Shrimp</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Fryer_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Icon_Pot_Rice</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Pot_Rice.png</t>
+  </si>
+  <si>
+    <t>Icon_Rice</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Rice.png</t>
+  </si>
+  <si>
+    <t>Icon_Shrimp</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Icon_Sushi_Shrimp</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Foods/Icon_Sushi_Shrimp.png</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Cut</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Cut.png</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Pot</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Pot.png</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Fan</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Fan.png</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Frier</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Frier.png</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Tray</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Tray.png</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -584,6 +667,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Nanum Gothic"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -627,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -635,6 +724,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -851,15 +945,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="84.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -867,7 +961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -875,7 +969,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
         <v>24</v>
       </c>
@@ -883,7 +977,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -891,7 +985,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
@@ -899,7 +993,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
@@ -907,7 +1001,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -915,7 +1009,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
         <v>14</v>
       </c>
@@ -923,7 +1017,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -931,7 +1025,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>16</v>
       </c>
@@ -939,7 +1033,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
         <v>107</v>
       </c>
@@ -947,7 +1041,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
         <v>108</v>
       </c>
@@ -955,7 +1049,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>135</v>
       </c>
@@ -963,7 +1057,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -971,7 +1065,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
@@ -979,7 +1073,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -987,7 +1081,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
@@ -995,7 +1089,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
         <v>137</v>
       </c>
@@ -1003,7 +1097,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -1011,7 +1105,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1019,7 +1113,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
         <v>71</v>
       </c>
@@ -1027,7 +1121,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
@@ -1035,7 +1129,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
         <v>75</v>
       </c>
@@ -1043,7 +1137,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
         <v>76</v>
       </c>
@@ -1051,7 +1145,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
         <v>77</v>
       </c>
@@ -1059,7 +1153,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" s="4" t="s">
         <v>73</v>
       </c>
@@ -1067,7 +1161,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2">
       <c r="A27" s="5" t="s">
         <v>78</v>
       </c>
@@ -1075,7 +1169,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
         <v>79</v>
       </c>
@@ -1083,7 +1177,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
         <v>80</v>
       </c>
@@ -1091,7 +1185,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2">
       <c r="A30" s="6" t="s">
         <v>113</v>
       </c>
@@ -1099,7 +1193,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
         <v>116</v>
       </c>
@@ -1107,7 +1201,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
         <v>114</v>
       </c>
@@ -1115,7 +1209,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
         <v>117</v>
       </c>
@@ -1123,7 +1217,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
         <v>118</v>
       </c>
@@ -1131,7 +1225,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
         <v>112</v>
       </c>
@@ -1139,7 +1233,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
         <v>120</v>
       </c>
@@ -1147,7 +1241,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
         <v>115</v>
       </c>
@@ -1155,7 +1249,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
         <v>119</v>
       </c>
@@ -1163,7 +1257,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2">
       <c r="A39" s="4" t="s">
         <v>111</v>
       </c>
@@ -1171,7 +1265,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
         <v>133</v>
       </c>
@@ -1179,7 +1273,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
         <v>138</v>
       </c>
@@ -1187,7 +1281,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2">
       <c r="A42" s="4" t="s">
         <v>145</v>
       </c>
@@ -1195,7 +1289,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2">
       <c r="A43" s="4" t="s">
         <v>143</v>
       </c>
@@ -1203,7 +1297,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2">
       <c r="A44" s="4" t="s">
         <v>147</v>
       </c>
@@ -1211,7 +1305,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2">
       <c r="A45" s="4" t="s">
         <v>141</v>
       </c>
@@ -1219,7 +1313,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2">
       <c r="A46" s="4" t="s">
         <v>148</v>
       </c>
@@ -1235,15 +1329,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="84.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1251,7 +1345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,7 +1353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1267,7 +1361,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1275,7 +1369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1283,7 +1377,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1291,7 +1385,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1299,7 +1393,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>105</v>
       </c>
@@ -1307,7 +1401,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1315,7 +1409,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +1417,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1331,7 +1425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>69</v>
       </c>
@@ -1339,7 +1433,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
         <v>67</v>
       </c>
@@ -1347,7 +1441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>104</v>
       </c>
@@ -1355,7 +1449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
         <v>68</v>
       </c>
@@ -1363,7 +1457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -1371,7 +1465,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -1387,15 +1481,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="84.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1403,136 +1497,246 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="B29" s="7"/>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
         <v>101</v>
       </c>
     </row>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -616,31 +616,36 @@
     <t>Icon_Cooking_Tile_Cut</t>
   </si>
   <si>
+    <t>Icon_Cooking_Tile_Pot</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Fan</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Frier</t>
+  </si>
+  <si>
+    <t>Icon_Cooking_Tile_Tray</t>
+  </si>
+  <si>
     <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Cut.png</t>
-  </si>
-  <si>
-    <t>Icon_Cooking_Tile_Pot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Pot.png</t>
-  </si>
-  <si>
-    <t>Icon_Cooking_Tile_Fan</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Fan.png</t>
-  </si>
-  <si>
-    <t>Icon_Cooking_Tile_Frier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Frier.png</t>
-  </si>
-  <si>
-    <t>Icon_Cooking_Tile_Tray</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Tray.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1637,39 +1642,39 @@
       <c r="A19" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>169</v>
+      <c r="B19" s="8" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>175</v>
+        <v>171</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B23" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>177</v>
       </c>
     </row>
@@ -1743,5 +1748,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -347,45 +347,6 @@
     <t>Assets/Resources_Addressable/Prefabs/Tiles/Wall_Tile.prefab</t>
   </si>
   <si>
-    <t>Image_Food_Poke</t>
-  </si>
-  <si>
-    <t>Image_Food_Hamburger_Set</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Potato</t>
-  </si>
-  <si>
-    <t>Image_Food_Pot_Rice</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Shirimp</t>
-  </si>
-  <si>
-    <t>Image_Food_Pot_Rice_2</t>
-  </si>
-  <si>
-    <t>Image_Food_Frier_Shirimp</t>
-  </si>
-  <si>
-    <t>Image_Food_Cut_Fish</t>
-  </si>
-  <si>
-    <t>Image_Food_Potato</t>
-  </si>
-  <si>
-    <t>Image_Food_Tuna</t>
-  </si>
-  <si>
-    <t>Image_Food_Rice</t>
-  </si>
-  <si>
-    <t>Image_Food_Fish</t>
-  </si>
-  <si>
-    <t>Image_Food_Shirimp</t>
-  </si>
-  <si>
     <t>MemoMat</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -646,6 +607,52 @@
   <si>
     <t>Assets/Resources_Addressable/Textures/CookingProperty/Icon_Cooking_Tile_Tray.png</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_Dummy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_Asian_Male</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_Asian_Female</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_European_Male</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_European_Female</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_African_Female</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Npc_African_Male</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_African_Female.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_African_Male.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_Asian_Female.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_Asian_Male.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_European_Female.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_European_Male.png</t>
   </si>
 </sst>
 </file>
@@ -721,7 +728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -734,6 +741,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1040,7 +1050,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>63</v>
@@ -1048,18 +1058,18 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1096,10 +1106,10 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1192,138 +1202,138 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="4" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1400,10 +1410,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1448,7 +1458,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>50</v>
@@ -1464,18 +1474,18 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1487,7 +1497,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1568,182 +1578,181 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="7" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="8" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="8" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="9" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="9" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="9" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B28" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" t="s">
         <v>172</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="7"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>95</v>
+      <c r="A30" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B30" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>100</v>
-      </c>
+      <c r="A31" s="1"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>101</v>
-      </c>
+      <c r="A36" s="1"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="202">
   <si>
     <r>
       <t>n</t>
@@ -653,6 +653,153 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Textures/Npc/Icon_Npc_European_Male.png</t>
+  </si>
+  <si>
+    <t>icon_move</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_dash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_right</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_turnback</t>
+  </si>
+  <si>
+    <t>icon_pickup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_putdown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_function</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>icon_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eset</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>icon_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lear</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>icon_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tart</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_left</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_repeat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_clear.png</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_dash.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_function.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_left.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_move.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_pickdown.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_pickup.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_repeat.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_reset.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_right.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_start.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_turnback.png</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1743,16 +1890,100 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1"/>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>197</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="214">
   <si>
     <r>
       <t>n</t>
@@ -700,6 +700,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>eset</t>
@@ -725,6 +726,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>lear</t>
@@ -750,6 +752,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>tart</t>
@@ -800,6 +803,42 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_turnback.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Npcs/African_Female.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Npcs/African_Male.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Npcs/Asian_Female.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Npcs/Asian_Male.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Npcs/European_Female.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Npcs/European_Male.prefab</t>
+  </si>
+  <si>
+    <t>African_Female</t>
+  </si>
+  <si>
+    <t>African_Male</t>
+  </si>
+  <si>
+    <t>Asian_Female</t>
+  </si>
+  <si>
+    <t>Asian_Male</t>
+  </si>
+  <si>
+    <t>European_Female</t>
+  </si>
+  <si>
+    <t>European_Male</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1481,6 +1520,54 @@
       </c>
       <c r="B46" s="4" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="220">
   <si>
     <r>
       <t>n</t>
@@ -839,6 +839,27 @@
   </si>
   <si>
     <t>European_Male</t>
+  </si>
+  <si>
+    <t>icon_cook</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Textures/BlockLogics/icon_cook.png</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/ItemHintUI.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemHintUI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemImage</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/ItemImage.prefab</t>
   </si>
 </sst>
 </file>
@@ -1147,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1568,6 +1589,22 @@
       </c>
       <c r="B52" s="4" t="s">
         <v>207</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>218</v>
+      </c>
+      <c r="B54" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -2058,17 +2095,25 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>192</v>
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>197</v>
       </c>
     </row>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="222">
   <si>
     <r>
       <t>n</t>
@@ -860,6 +860,13 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/WorldUI/Elements/ItemImage.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/FunctionButtonInteractable.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionButtonInteractable</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1200,410 +1207,418 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="5" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>63</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>54</v>
+        <v>122</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="5" t="s">
+    <row r="18" spans="1:2">
+      <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="4" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B27" s="4" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>110</v>
+        <v>100</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B41" s="5" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="5" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="4" t="s">
-        <v>208</v>
+        <v>135</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B53" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
         <v>218</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>219</v>
       </c>
     </row>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="223">
   <si>
     <r>
       <t>n</t>
@@ -374,10 +374,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Resources_Addressable/Materials/Logic/TempMat.mat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>RotateBackBlockLogic</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -659,15 +655,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>icon_dash</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>icon_right</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_turnback</t>
   </si>
   <si>
     <t>icon_pickup</t>
@@ -867,6 +856,20 @@
   </si>
   <si>
     <t>FunctionButtonInteractable</t>
+  </si>
+  <si>
+    <t>icon_dash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_turnback</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/DashMat.mat</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Materials/Logic/RotateBackMat.mat</t>
   </si>
 </sst>
 </file>
@@ -1208,10 +1211,10 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1272,7 +1275,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>63</v>
@@ -1280,18 +1283,18 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1328,10 +1331,10 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1424,202 +1427,202 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B55" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1699,7 +1702,7 @@
         <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1739,7 +1742,7 @@
         <v>67</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1768,10 +1771,10 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1864,272 +1867,272 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>141</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>143</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>179</v>
+        <v>219</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>181</v>
+      <c r="A38" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="B38" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\dev\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-5685" windowWidth="16440" windowHeight="28320"/>
   </bookViews>
   <sheets>
     <sheet name="GameObject" sheetId="12" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="225">
   <si>
     <r>
       <t>n</t>
@@ -870,6 +870,25 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Materials/Logic/RotateBackMat.mat</t>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>utLine</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/OutLine/OutLine.prefab</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1623,6 +1642,14 @@
       </c>
       <c r="B55" t="s">
         <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B56" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -1786,7 +1813,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -2135,6 +2162,10 @@
         <v>194</v>
       </c>
     </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\dev\ProjectVCG\Assets\Resources\Xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\ProjectVCG\Assets\Resources\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="227">
   <si>
     <r>
       <t>n</t>
@@ -889,6 +889,13 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/Tiles/OutLine/OutLine.prefab</t>
+  </si>
+  <si>
+    <t>BlockSlot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/BlockSlot.prefab</t>
   </si>
 </sst>
 </file>
@@ -964,7 +971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -982,6 +989,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1197,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1650,6 +1658,14 @@
       </c>
       <c r="B56" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B57" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="231">
   <si>
     <r>
       <t>n</t>
@@ -134,10 +134,6 @@
   </si>
   <si>
     <t>NPCMessagePopup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ButtonInteractable</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -896,6 +892,22 @@
   </si>
   <si>
     <t>Assets/Resources_Addressable/Prefabs/BlockSlot.prefab</t>
+  </si>
+  <si>
+    <t>GrapAndPokeObject</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/GrapAndPokeObject.prefab</t>
+  </si>
+  <si>
+    <t>GrapAndPokeObject_Function</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/GrapAndPokeObject_Function.prefab</t>
+  </si>
+  <si>
+    <t>ButtonInteractable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1205,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1225,23 +1237,23 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>24</v>
+        <v>230</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1249,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1257,7 +1269,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1265,7 +1277,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1273,7 +1285,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1281,7 +1293,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1289,7 +1301,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1297,31 +1309,31 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1329,7 +1341,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1337,7 +1349,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1345,7 +1357,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1353,15 +1365,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1369,303 +1381,319 @@
         <v>20</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" t="s">
         <v>215</v>
-      </c>
-      <c r="B55" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" t="s">
         <v>223</v>
-      </c>
-      <c r="B56" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B57" t="s">
         <v>225</v>
       </c>
-      <c r="B57" t="s">
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
         <v>226</v>
+      </c>
+      <c r="B58" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>228</v>
+      </c>
+      <c r="B59" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1697,7 +1725,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1705,7 +1733,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1713,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1721,7 +1749,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1729,7 +1757,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1737,15 +1765,15 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1753,7 +1781,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1761,7 +1789,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1769,55 +1797,55 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
         <v>89</v>
-      </c>
-      <c r="B16" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1846,336 +1874,336 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>138</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>144</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>148</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" t="s">
         <v>211</v>
-      </c>
-      <c r="B41" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:2">

--- a/Assets/Resources/Xlsx/AssetAddress.xlsx
+++ b/Assets/Resources/Xlsx/AssetAddress.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="239">
   <si>
     <r>
       <t>n</t>
@@ -909,12 +909,37 @@
     <t>ButtonInteractable</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Cooking_Tile_Cut</t>
+  </si>
+  <si>
+    <t>Cooking_Tile_Pot</t>
+  </si>
+  <si>
+    <t>Cooking_Tile_Frier</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cooking_Tile_Tray</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Elements/Cooking_Tile_Cut.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Elements/Cooking_Tile_Frier.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Elements/Cooking_Tile_Pot.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Resources_Addressable/Prefabs/Tiles/Elements/Cooking_Tile_Tray.prefab</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -941,6 +966,13 @@
       <name val="Nanum Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -956,7 +988,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -979,11 +1011,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1002,6 +1054,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1217,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="31.140625" customWidth="1"/>
@@ -1688,12 +1746,44 @@
         <v>227</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" ht="13.5" thickBot="1">
       <c r="A59" t="s">
         <v>228</v>
       </c>
       <c r="B59" t="s">
         <v>229</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B61" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
